--- a/光伏配储项目/电价数据/2026/塘朗站.xlsx
+++ b/光伏配储项目/电价数据/2026/塘朗站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.7710399999999999</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.3846</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.03266</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.8623500000000001</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.59275</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.73722</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.77639</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.44268</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.46035</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43242</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42709</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.42536</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.41336</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38815</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.42868</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41717</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39509</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38821</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.42097</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39547</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42486</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41788</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42805</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44794</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.50304</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.40132</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.32795</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.35128</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.37439</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.3519</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.13091</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.14405</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.3382</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.14888</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.08473</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.12305</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.48513</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.2112</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.31439</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.05221</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.9775199999999999</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>1.54715</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.1491</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.22166</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23074</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.236</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.21995</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.8611</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.27993</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.47402</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.15687</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.34836</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.36217</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.29046</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.29569</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.48379</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.6482899999999999</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.73864</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.86198</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.7305700000000001</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.53854</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.43116</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.43629</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.6577999999999999</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.22584</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.8334</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.56297</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.41387</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.64278</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.80214</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.04521</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.1018</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.68848</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.281</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.8699600000000001</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.79613</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.75666</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.5174500000000001</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.47918</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.4687</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.41557</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.42519</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.7078300000000001</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.7672</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.86983</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.914</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.49354</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.51375</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.50184</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.50208</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.48439</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39899</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.46657</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33616</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.36515</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.35054</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.36606</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.34967</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.40511</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.8550800000000001</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.7004</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.79583</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.45335</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.43387</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.377</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.34739</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.42661</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.50876</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.35475</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.33939</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35661</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.33205</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.38135</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.30246</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.37841</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.51401</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.78576</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.9999600000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.3371499999999999</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.52901</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.89603</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.85162</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.50422</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.7356900000000001</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>1.55335</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>1.09692</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>1.03181</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.47398</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.5495399999999999</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.50312</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.52488</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.90939</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.62193</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.9095</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>1.21109</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.46612</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.17711</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.06436</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.5127</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.41507</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.57075</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.34973</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.39999</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.95672</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.29227</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.9009299999999999</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.35986</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.41395</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.28683</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.07729</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.79014</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.8103899999999999</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.44866</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.42785</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.4433</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33349</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.37546</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33457</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.50705</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48648</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.37782</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.44721</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.41376</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.3683</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.38895</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.38243</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.36292</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.42718</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44254</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33562</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36983</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.39515</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.3675</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.3609</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.35153</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.3622</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.38286</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.47147</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.4436</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.43739</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.39398</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.35261</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36725</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34732</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.47684</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.6162799999999999</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.84766</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.77787</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.7187899999999999</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.24222</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.33164</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.37687</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.41097</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.42468</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.56599</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.5103</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.82978</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.41238</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.60348</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.7301799999999999</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.81817</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.52884</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.54664</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.7979400000000001</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>1.18854</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.6800900000000001</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.60278</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.49427</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.46037</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.4238</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.7571</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.5195700000000001</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.50543</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.5709</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.59709</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.54692</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.5670299999999999</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>1.2614</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.6155499999999999</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>1.06184</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.49534</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.5287999999999999</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5717100000000001</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.9063600000000001</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.95087</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>1.36765</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.7559199999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.7694099999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.62163</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.83412</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.60915</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.8571299999999999</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.5625800000000001</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>1.19869</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.82574</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.5616100000000001</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.48572</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.61922</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.50776</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.45639</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.39723</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36204</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34191</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.5213</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.49319</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.44428</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.38906</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.38904</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.36686</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.35876</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.38724</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.38539</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.36125</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.44819</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34837</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.35727</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.35836</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33882</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35087</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.38492</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.38825</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34845</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.37459</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34388</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.3931</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.5047</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.6864600000000001</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.34045</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.57797</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.78923</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.71704</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.8009500000000001</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>1.23086</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.62015</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>1.30926</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>1.15041</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>1.06134</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.85024</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>1.32834</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.86448</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.35716</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.44757</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.6023999999999999</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.40801</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.33523</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.48114</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.40618</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.39831</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.8130599999999999</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.8206100000000001</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.7287899999999999</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>1.27077</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>1.26511</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.42533</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.49343</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45023</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.46096</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.39939</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.47352</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.5212</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.9407799999999999</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.83116</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>1.27456</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.89025</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.7987799999999999</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50068</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.73049</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.68667</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.59749</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.50649</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.34624</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.34143</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31397</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.31669</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.69492</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.80459</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.38239</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.36145</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.36134</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3291</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32804</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33215</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32074</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31902</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31609</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31641</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31945</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31605</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.31076</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.31012</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31339</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31468</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.4362799999999999</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.33075</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.32579</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.30964</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.3038</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.30498</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.2047</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.42155</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.38675</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.22639</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.15473</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.28945</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.29386</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.36215</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.19453</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.42008</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.39624</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.06516</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.38249</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.37975</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22629</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.39339</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.21278</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.06566</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.09772</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.0147</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.004</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.19536</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.27038</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.2976</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33572</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33585</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.33317</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.37523</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38109</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.37555</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.38712</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39073</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.45984</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.37011</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.38915</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.39052</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.48298</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34428</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35362</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.34248</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36549</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.57214</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.37503</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.39456</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.37904</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.37267</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.34104</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.29862</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.2789</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.24992</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.33611</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.32749</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.30947</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.305</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.28977</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.28987</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.28511</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.32779</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.31627</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.33006</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.34448</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.30373</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10285</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04362</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.0441</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04476</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.35844</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01545</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.21658</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.05443</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.29072</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.20672</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.08398</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.28995</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.04529</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04423</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.07072000000000001</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.06895999999999999</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04984</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28994</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29678</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.34676</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33048</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.3232</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.3113</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31029</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.34406</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.3203</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27071</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29731</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38768</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37931</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.45494</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41845</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41528</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.38579</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.2943</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31094</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31343</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31269</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34628</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.7851900000000001</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142100000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.8628899999999999</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.29622</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88751</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18709</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8791</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>1.26666</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33086</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.03292</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53079</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.79099</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.791</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.77298</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.77755</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87387</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49315</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.3999</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44995</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.207</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62186</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45582</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.4495</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.41962</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.34587</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39814</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.40786</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.42479</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32892</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.33918</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.38069</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44896</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.3803</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.55228</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.40606</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.58153</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.70141</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.8755299999999999</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.46572</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.38583</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.54538</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.42986</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.80276</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.5563899999999999</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.85077</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87498</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.34076</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.4131</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.61275</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30222</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.29234</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.6185499999999999</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.59105</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>1.10562</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31056</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35164</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.33358</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31907</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.31951</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.33411</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.31777</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.30762</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.30106</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29586</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31112</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.30896</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31044</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.2814</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.30188</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.31377</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.34688</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.32846</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33071</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.323</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.3249</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.3833</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.38535</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.4168</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.38719</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.37017</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.35396</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.34611</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.91289</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.34738</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.43925</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.40266</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.431</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3857</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.3502</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.35291</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.33888</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.33838</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.33296</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.34606</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.33457</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.37264</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.45342</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.33201</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.34084</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.35245</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.34712</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.30526</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.32361</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.32769</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.32991</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.31057</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31277</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.31596</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.30149</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.19468</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.3043</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30791</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.34316</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.31134</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.27296</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.19731</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29876</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.31948</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.2807</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.30832</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.30878</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.34658</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.35457</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.30688</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29936</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.30777</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.3108</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.30774</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.30775</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.2934</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29398</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.29806</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.30487</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.28797</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25301</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.31035</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.32432</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.32638</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27364</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.33308</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.29976</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.33794</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.40517</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.41915</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.34265</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.43744</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.32442</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.39571</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.37524</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.37279</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.5195299999999999</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8598300000000001</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.43679</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13208</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.68244</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.7725599999999999</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.6343</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.48873</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.38966</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.48694</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.4277</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.41115</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.40242</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.4023</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.45412</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.40261</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.42291</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.38386</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.42372</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.3826</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.3935</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.4104</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.38621</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.41424</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.39889</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.40265</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.40585</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.38741</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.38839</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.4844</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.3556</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.29904</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.33945</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.30444</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.33237</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.30535</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.29805</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.51812</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.35516</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.20941</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24785</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.29973</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.15435</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.27294</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.27514</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.01155</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.33391</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30111</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.25923</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.25207</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.30786</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.28132</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.29081</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.30436</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.28843</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.30995</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.31753</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.31612</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.30996</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.32554</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38382</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.38044</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.35218</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.35246</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.33946</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.53626</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.42618</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.77359</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.42732</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.45301</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.43585</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.36595</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.35342</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.31831</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.30366</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.38241</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.31769</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.2923</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.32734</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.28728</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.2892</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.27896</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.28791</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.30609</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.30443</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.30546</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.27381</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.27395</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.31303</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.30094</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.22783</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.23202</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.30959</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.34506</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.31482</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31042</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.2311</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.26698</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.25934</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.31281</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23036</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.25597</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.34945</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.33086</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.38762</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24978</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.28732</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.32319</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.29009</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.3179</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.30992</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.30677</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28961</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.26169</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.3204</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.3639</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.26955</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.30977</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.28783</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.3305</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.3103</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.46811</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.35356</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.4094</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31833</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.35584</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.43278</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.33223</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.33555</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.34319</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.36155</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.41007</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.37268</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.3669</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.37387</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.37192</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.41456</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.40295</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.40728</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.43659</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.39285</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.38103</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.38279</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.34015</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.32254</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3316</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.32643</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.48121</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.38121</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.4285</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.39439</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.38799</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.36079</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.35973</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.37063</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.36257</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.36277</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.37062</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.35399</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.33651</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.3342</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.33231</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.32856</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.3327</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.32855</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.33763</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.41273</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.36037</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.34502</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.33054</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.33171</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.33856</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.32877</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.29874</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.29642</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.97335</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.72712</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.34722</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.27921</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30088</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.30132</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.31807</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31766</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.31354</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.23934</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.31192</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.30242</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.47518</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.41574</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.5251</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.49477</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.39973</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.33281</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.71028</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.78513</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.37321</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.39327</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34064</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.39183</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.73934</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.9108099999999999</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.66488</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.94799</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>1.13026</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.37744</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.37037</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.40899</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.40725</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.40254</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.63602</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.33983</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.3425</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.44682</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.40236</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.35689</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.36647</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.33847</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.34628</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.33479</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.45177</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.46468</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.36281</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34911</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.34286</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.32928</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.33335</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.33543</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.33023</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.33524</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.3307</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.32672</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.35736</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.3724</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.36539</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.35916</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.42185</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.33034</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.7784099999999999</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.8968200000000001</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.8789</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.44168</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.7895800000000001</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.46725</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>1.14674</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.87158</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.85526</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>1.1149</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.82602</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>1.30601</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>1.1761</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>1.21119</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.77639</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>1.23137</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>1.42562</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.59639</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>1.38172</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>1.27115</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>1.42737</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>1.6971</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>1.55194</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>1.43086</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>1.55153</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>1.22418</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>1.5021</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.89338</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>1.74491</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.6770499999999999</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>1.21708</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.68355</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.6516000000000001</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.7391599999999999</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.66903</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.66275</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>1.17021</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.78901</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>1.49181</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.7680900000000001</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.74999</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>1.02531</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.69797</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.63491</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.59382</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.5069399999999999</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.50197</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.23864</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.36738</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.35107</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.32755</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.33903</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.31013</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.33627</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.6628099999999999</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.30373</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.52743</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.39159</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.41192</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.31987</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33148</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.34764</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.30748</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.35809</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32646</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32132</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.3208</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.31293</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.36808</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.29382</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.28136</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31201</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.31519</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.29355</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.29844</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.3093399999999999</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.3022</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.30605</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32783</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.34786</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.36969</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.98227</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.34075</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.45684</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.3413</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.32932</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.3132799999999999</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.33109</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.3309</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.30831</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.3241</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.27541</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.33299</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.31097</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.31726</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.31954</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.32623</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.33169</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32686</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.30771</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.30945</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.77078</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.33475</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>1.07827</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>1.36451</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>1.00536</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.49467</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.3288</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.35285</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.36389</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.33753</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.33682</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.76413</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.36677</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.7597</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.34821</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.33848</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.3494</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.35219</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.35603</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.356</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.34663</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.35308</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.3569</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.31895</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.34213</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.3191000000000001</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34173</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.32719</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.34252</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3425299999999999</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.34349</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.34296</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.34216</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.33137</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34152</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.33837</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.26076</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.33915</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.3324</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.33263</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.32539</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.3165</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33183</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.33214</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.32315</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.3221</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.33716</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.33374</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.33361</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.32441</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.32792</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.31656</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.29864</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.3172</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32267</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.31388</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.32278</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.3154</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.32275</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.32011</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32858</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31752</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.36968</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31914</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.7094400000000001</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>1.23051</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.41191</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.5287200000000001</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.41626</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.38226</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.40761</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.4814</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.34027</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.36041</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.33274</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34865</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.34885</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.56664</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.37737</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.34584</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35174</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.34329</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.37803</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.3474</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.35088</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.39557</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.36789</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.47138</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.41045</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.3688</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.40086</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.5808099999999999</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.36792</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64949</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42295</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.5924400000000001</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.5746</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.8367599999999999</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.34249</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.6819400000000001</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35137</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.33195</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.4032</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.35816</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.35409</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.35124</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.3509</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.35407</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.35016</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.34833</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.35102</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.34488</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.35203</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.34757</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.34817</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.34412</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.35152</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.35185</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.33972</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35082</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.34856</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.36039</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.35792</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.37193</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.34852</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.34323</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.34392</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>1.20321</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.44441</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.74683</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.5127200000000001</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.77162</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.43649</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.5957899999999999</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.8378099999999999</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.37797</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.29985</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.28607</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32286</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.33473</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.30578</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.33482</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.34427</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.61771</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.34151</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.338</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.40859</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.3406</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.65723</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.51937</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.78291</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.68257</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>1.12842</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.64506</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.6220800000000001</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.34501</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.84141</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.65091</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.82936</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>1.1745</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>1.16844</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>1.20458</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.9529500000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.9107499999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.24114</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.7965399999999999</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.03775</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.80726</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>1.61201</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.79745</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.70868</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>1.22682</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>1.15305</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.68343</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.39268</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.36349</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.34826</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34576</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.44728</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.51639</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46566</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.60058</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.39126</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.38085</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.38521</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.38503</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.39069</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.37815</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3867</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.39011</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.38836</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.37653</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.39028</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.36723</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.3887</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.36899</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.37033</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.38575</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.37211</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.40608</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.40905</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.49066</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.45012</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.41402</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.44762</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41268</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.57129</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>1.17013</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.8392200000000001</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>1.21741</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>1.25406</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>1.59072</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>1.42656</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>1.36203</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>1.34699</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>1.3547</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>1.54754</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>1.55045</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>1.5745</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>1.70202</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>1.55459</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>1.46638</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>1.49775</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>1.48885</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>1.56826</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>1.5416</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>1.54952</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.5319700000000001</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.5309700000000001</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.83504</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.33927</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34117</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.3961</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.33655</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.35432</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.39879</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.38618</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.8167000000000001</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.82078</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.82586</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.81588</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.82263</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.81432</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.82555</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>1.44972</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>1.41337</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>1.46216</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>1.46221</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>1.49315</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>1.60263</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>1.70312</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>1.79134</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>1.56905</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.72551</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.75217</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.7764500000000001</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.7075900000000001</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.76387</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.61653</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.66465</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.8024600000000001</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.62049</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.43972</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.43657</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.42981</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.39253</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.49415</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.40024</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.41038</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.42004</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.42659</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.41651</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.41183</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.40825</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.37693</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.40659</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.3691</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.37545</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.4478</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.36121</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.35523</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.35228</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.34908</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.35195</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.35806</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.35748</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.36222</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37163</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.34677</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.35349</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.34725</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37158</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39424</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.35638</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.39139</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.37612</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.84589</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.8329</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.41545</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>1.33364</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>1.34086</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>1.36796</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>1.54573</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>1.51703</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>1.514</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>1.5351</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>1.52419</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>1.72035</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>1.53615</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.6119199999999999</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.57275</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.62112</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>1.16703</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.16525</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.27014</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33833</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.3419700000000001</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.34233</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.3365</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.35455</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>1.37592</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>1.37522</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.54344</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.8336399999999999</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.32946</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.4618</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.85846</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.8418099999999999</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.84622</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>1.38831</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.81538</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>1.34443</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.8091699999999999</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.40555</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.40186</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.36761</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.36404</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.35225</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.35663</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35384</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.36992</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.32788</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.35365</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.30742</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.3278</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.32364</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.29184</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.44985</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.8254</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.35057</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.81509</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.33732</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.30245</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.27893</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.33147</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.26349</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.2611</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.3024</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.26097</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.34356</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.30148</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.24952</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.28563</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.29321</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.30255</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.29356</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.29797</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.24234</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.24145</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.23492</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.32002</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.2738</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.30634</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.2298</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.34182</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.30519</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.30004</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.17933</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.28156</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.24966</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.26965</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.26556</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.26144</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.08801</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.31569</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.26335</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.25909</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.03215</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.2889</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.28223</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.20164</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.28134</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.3115</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.25343</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.27175</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25731</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.24207</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.27626</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.2849100000000001</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.2729</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.32165</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.31486</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.33705</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.33463</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.34468</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3597</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.33943</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.35258</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.38186</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.37364</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.4445</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.34614</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.33569</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.34905</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.32843</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.33417</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.42995</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.40223</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.33389</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.29924</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.32866</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.29895</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.31719</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.29717</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.58263</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.32486</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.32464</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.3259</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.25744</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.28708</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.28272</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.2248</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.28151</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.23681</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.22345</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.22694</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.22692</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.22385</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.22385</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.2257</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.27701</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.2198</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.22385</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.22415</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.27532</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.22359</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.22339</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.23078</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.15347</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.26532</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.20011</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01143</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00043</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.00024</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04957</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.14515</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02125</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03957</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.01546</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04286</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04074000000000001</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04859</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04824000000000001</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02923</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.0494</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>3e-05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.27425</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04964</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.0493</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.03835</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.01943</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04963</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03619</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.20112</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.26461</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.28806</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.2789700000000001</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.30265</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.30686</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22812</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.30913</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.32644</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.34218</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.33516</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.33809</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.30827</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.33591</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.33994</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.33876</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.33564</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.36207</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.35092</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.34625</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.34167</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.34095</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.33291</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.3434</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.32698</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.7070299999999999</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.60964</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.38025</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.40148</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.38625</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.41447</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.35545</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.30068</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.29694</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.24172</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.29413</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.27884</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.23892</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.22313</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.25646</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.24217</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.26911</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.28046</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.43519</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.3485</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.33727</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.34478</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.24814</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.35946</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.62913</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.80384</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.87541</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8507400000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.3257</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.38052</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.75759</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.62439</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.71417</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.73065</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.29838</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.30047</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.38541</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.38163</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.18358</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.03791</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.37836</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.37598</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.75467</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.33664</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.30643</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.34363</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.31241</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.3377</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.37986</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.37208</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.37453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.37619</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.47133</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.79242</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.77215</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.80061</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.8121</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.77054</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.79432</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.78467</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.81372</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>1.20088</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>1.5732</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>1.59821</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>1.16287</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>1.24674</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.7704</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.83909</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.83729</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.8416</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.93888</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.7283099999999999</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.76636</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.7319099999999999</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.35335</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.37074</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.36026</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.3601</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.45794</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.59278</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.6063500000000001</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.55559</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.49219</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.45171</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.39531</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.38455</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.37935</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.36608</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.3464</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33208</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32163</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.31306</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.4625</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.31419</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.30713</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.30825</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.26312</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33238</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.35798</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.45248</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.46126</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.35922</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.37596</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.32046</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.32867</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.41681</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.37361</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.44109</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>1.21192</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.8359</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.8114</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>1.63143</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.7754</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.76336</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>1.22918</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.7802899999999999</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.74302</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.3459</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.75949</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.7407</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.77616</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.74338</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.7345</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.78747</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.34972</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.79216</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.78983</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>1.19863</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.74946</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.34717</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.34171</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.33935</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.33749</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.3414</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.6244</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.7877799999999999</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.7896599999999999</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.76979</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>1.61639</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>1.62335</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.758</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.7832</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.82353</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.80979</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.7951699999999999</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.77108</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.79515</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>1.29014</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>1.29659</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.7522799999999999</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.40117</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.38277</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.34928</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.35213</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.33544</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33345</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.41503</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.41724</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.4027</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.38543</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.3788</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.37484</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.37243</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.35386</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.35592</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.34862</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.3483</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34408</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.3453</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34313</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.33963</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.34877</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.32642</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.32999</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.33989</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.33244</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.34769</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3484</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.34208</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.39643</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.36137</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.53186</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.74699</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.9429999999999999</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>1.38283</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.85827</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>1.62399</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>1.19686</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.77052</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.77837</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.81225</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.77611</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.80896</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.77308</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.72812</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.85505</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.83286</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.84909</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.8476900000000001</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.8082999999999999</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.7655700000000001</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.8507400000000001</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.75113</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.74879</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.83269</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.76406</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.75429</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.75879</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.74812</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.7688200000000001</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.76888</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>1.31951</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>1.00253</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>1.32571</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.68599</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>1.58662</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>1.72025</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>1.56423</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>1.73332</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.54299</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>1.38767</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>1.44645</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.44404</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.5906399999999999</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.6630499999999999</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.7668400000000001</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.44919</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.4183</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.41243</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.374</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.3759</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.23172</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.34063</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.34894</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.37745</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.37277</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.36547</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.35263</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.3635</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.35719</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.35563</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.352</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.34386</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.34348</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.33647</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.31754</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.3366</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.32904</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.33871</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.33526</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.34536</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.36521</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.34782</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.3545</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.34909</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.34581</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.37887</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.36338</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.3539</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43496</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.37281</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.35336</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31055</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.82087</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.39413</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.52539</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.39925</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.2926</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.54264</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.4232</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.37902</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.46406</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31621</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33661</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33353</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34174</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32487</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34422</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.34291</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.36605</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.3634</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>1.16956</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>1.18312</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>1.16863</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>1.39272</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>1.37199</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>1.37262</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>1.41637</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>1.40992</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>1.24995</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.76426</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.1145</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.56586</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.65608</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.97668</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.61485</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.47086</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.13125</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.90576</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.94543</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.7775700000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.6109199999999999</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.6183099999999999</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.41329</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.35628</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.35335</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.29948</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.35507</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.34499</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.33462</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.32818</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.34127</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.34106</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.3306</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33637</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.33354</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.20588</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.32439</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.32385</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.3315</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.34439</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.33962</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33322</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.3737</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.37366</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.3513</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.3372</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.33629</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.35827</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.33386</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.3466</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.34976</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.33493</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.84723</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>1.18842</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.47869</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.8582000000000001</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.89459</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.51432</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.8437</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.48306</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.45261</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.94959</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.57451</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>1.39678</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.8591599999999999</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>1.23239</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.4787</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.8507</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.9805900000000001</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.8531</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.49957</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34822</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.34026</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.41755</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.40287</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.35992</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.42906</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.8743300000000001</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.76139</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.41242</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.36427</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.5437799999999999</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.9638300000000001</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.48448</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.56026</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>1.26885</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.5878099999999999</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.88728</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.45396</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.6212000000000001</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.30458</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.56938</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.6106</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.57347</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.82741</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39613</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.42302</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.40135</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.36708</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38365</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.46377</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.35984</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.34267</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.11827</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.76032</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.5539700000000001</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.58772</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.82899</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.36393</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.43619</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.37012</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37959</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.36823</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.36654</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.36604</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.36224</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.36584</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.3659</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.36559</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.36108</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.357</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.35793</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.35675</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.34724</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35631</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35111</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.36907</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.35621</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34377</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.34574</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.35051</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.35463</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.37386</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.36265</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.6771</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.41047</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.34716</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.34923</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.44296</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.34383</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.35422</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.60001</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.38547</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.4349</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.34775</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.85078</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.66013</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.33832</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32283</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3369</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.34988</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32337</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35614</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35819</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32965</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.35397</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.34516</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.34844</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.3725</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.43811</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.42553</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.40192</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.38198</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35385</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.36139</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.43227</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.45131</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.56212</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.51387</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.48465</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.4351</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38179</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.42806</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.39344</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.90415</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.09824</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.8434199999999999</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.50039</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.61414</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.7076699999999999</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.6535700000000001</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.44717</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.35498</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35521</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.3561</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.3567</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.3482</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.41032</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.38341</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.36122</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37144</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.37289</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36493</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.36676</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.36032</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.36546</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.35829</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.36093</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.36442</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.35116</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.35411</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.35512</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.35147</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.35387</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.35257</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.34637</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.34149</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.35282</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.34731</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.34762</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.31191</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31729</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.31724</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17554</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29453</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31058</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14522</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19787</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14195</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.29126</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04461</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12175</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22657</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26672</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.24801</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14403</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.33087</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.37973</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.3683999999999999</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.38182</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.37396</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.1525</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.35594</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.38313</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.38268</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.37124</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.19626</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.36467</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.36415</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.38708</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.36246</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.40093</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.36399</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.36009</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.37662</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33672</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.39981</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.4079100000000001</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.42038</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.38384</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.84223</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.6213</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.4751</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>1.09465</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.3427</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.40947</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.36178</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.49689</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.43905</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.38058</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.3891</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.43638</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38318</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.48932</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.3952</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.48805</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.4402799999999999</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.44323</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.46164</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.38303</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.38153</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38275</v>
       </c>
     </row>
   </sheetData>
